--- a/input/industry/Specific_Consumption_BAT.xlsx
+++ b/input/industry/Specific_Consumption_BAT.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C2083C-3FD2-4103-8E24-9CE9DF982E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B3AE8F-0350-4D56-859A-22783A72D934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18570" yWindow="1185" windowWidth="21885" windowHeight="14730" tabRatio="788" firstSheet="14" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30810" yWindow="1470" windowWidth="20175" windowHeight="13230" tabRatio="788" firstSheet="17" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="steel" sheetId="9" r:id="rId1"/>
@@ -28,13 +28,18 @@
     <sheet name="ethylene_classic" sheetId="22" r:id="rId18"/>
     <sheet name="propylene" sheetId="15" r:id="rId19"/>
     <sheet name="propylene_classic" sheetId="23" r:id="rId20"/>
-    <sheet name="aromatics" sheetId="16" r:id="rId21"/>
-    <sheet name="aromatics_classic" sheetId="24" r:id="rId22"/>
-    <sheet name="Info" sheetId="2" r:id="rId23"/>
+    <sheet name="olefins" sheetId="27" r:id="rId21"/>
+    <sheet name="olefins_classic" sheetId="28" r:id="rId22"/>
+    <sheet name="aromatics" sheetId="16" r:id="rId23"/>
+    <sheet name="aromatics_classic" sheetId="24" r:id="rId24"/>
+    <sheet name="Info" sheetId="2" r:id="rId25"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId24"/>
+    <externalReference r:id="rId26"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_CTVL0014bc30cd650ab4ee9a6bbd5bf2e9a7c20" localSheetId="24">Info!$E$79</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -56,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="128">
   <si>
     <t>Country</t>
   </si>
@@ -184,12 +189,6 @@
 0,08 MWh/t elec for mechanical work = 0.288 GJ/t</t>
   </si>
   <si>
-    <t>Total energy demand as energy efficincy potential</t>
-  </si>
-  <si>
-    <t>50.6 GJ/t</t>
-  </si>
-  <si>
     <t>Distribution of electricity and heat demand according to the specific "usual" demand</t>
   </si>
   <si>
@@ -197,9 +196,6 @@
   </si>
   <si>
     <t>alu_sec</t>
-  </si>
-  <si>
-    <t>2.5 GJ/t</t>
   </si>
   <si>
     <t>Electricity and heat demand same as for the "usual" demand</t>
@@ -336,14 +332,7 @@
     <t>See Specific_Consumption.xlsx</t>
   </si>
   <si>
-    <t>ethylene-, propylene-, aromatics_classic</t>
-  </si>
-  <si>
     <t>https://www.bmwk.de/Redaktion/DE/Downloads/E/energiewende-in-der-industrie-ap2a-branchensteckbrief-chemie.pdf?__blob=publicationFile&amp;v=4</t>
-  </si>
-  <si>
-    <t>elec: 0
-fuel: 12 GJ/t</t>
   </si>
   <si>
     <t>copper_prim</t>
@@ -426,7 +415,92 @@
     <t>Achtelik, Christian; Schimmel, Matthias; Rhiemeier, Jan-Martin</t>
   </si>
   <si>
-    <t>chlorine, ammonia, ammonia_classic, methanol, methanol_classic, ethylene-, propylene-, aromatics</t>
+    <t>chlorine, ammonia, ammonia_classic, methanol, methanol_classic, ethylene, propylene, aromatics, olefins</t>
+  </si>
+  <si>
+    <t>ethylene-, propylene-, olefins_classic</t>
+  </si>
+  <si>
+    <t>Worrell, E., Price, L., Neelis, M., Galitsky, C. &amp; Zhou, N. World Best Practice Energy Intensity Values for SelectedIndustrial Sectors, 2007.</t>
+  </si>
+  <si>
+    <t>elec:1 GJ/t</t>
+  </si>
+  <si>
+    <t>total 12 GJ/t</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ren, T., Patel, M. &amp; Blok, K. Olefins from conventional and heavy feedstocks: Energy use in steam cracking and alternative processes. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Energy </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">31, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>425–451; 10.1016/j.energy.2005.04.001 (2006).</t>
+    </r>
+  </si>
+  <si>
+    <t>aromatics_classic</t>
+  </si>
+  <si>
+    <t>total 7 GJ/t</t>
+  </si>
+  <si>
+    <t>https://dechema.de/dechema_media/Downloads/Positionspapiere/Technology_study_Low_carbon_energy_and_feedstock_for_the_European_chemical_industry.pdf</t>
+  </si>
+  <si>
+    <t>The European Chemical Industry Council</t>
+  </si>
+  <si>
+    <t>Low carbon energy and feedstock for the European chemical industry</t>
+  </si>
+  <si>
+    <t>Table 11</t>
+  </si>
+  <si>
+    <t>Bazzanella, Alexis Michael, Ausfelder, Florian</t>
+  </si>
+  <si>
+    <t>50.6 GJ/t
++ 3.9 GJ/t</t>
+  </si>
+  <si>
+    <t>Total energy demand as energy efficincy potential
+total BAT value for processing</t>
+  </si>
+  <si>
+    <t>2.5 GJ/t
++ 3.9 GJ/t</t>
   </si>
 </sst>
 </file>
@@ -436,7 +510,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,6 +536,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -582,44 +664,25 @@
       <sheetName val="ethylene_classic"/>
       <sheetName val="propylene"/>
       <sheetName val="propylene_classic"/>
+      <sheetName val="olefins"/>
+      <sheetName val="olefins_classic"/>
       <sheetName val="aromatics"/>
       <sheetName val="aromatics_classic"/>
       <sheetName val="Info"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4">
-        <row r="2">
-          <cell r="B2">
-            <v>55.470000000000006</v>
-          </cell>
-          <cell r="C2">
-            <v>52.2</v>
-          </cell>
-          <cell r="D2">
-            <v>3.27</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="2">
-          <cell r="C2">
-            <v>1.8</v>
-          </cell>
-          <cell r="D2">
-            <v>9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
       <sheetData sheetId="12">
         <row r="2">
           <cell r="B2">
@@ -630,9 +693,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
       <sheetData sheetId="16">
         <row r="2">
           <cell r="C2">
@@ -643,10 +706,12 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22">
         <row r="2">
           <cell r="C2">
             <v>28.22</v>
@@ -656,8 +721,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1172,6 +1237,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1462,9 +1533,15 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33765430-3FBC-44EA-882E-28F273195AF2}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1479,6 +1556,9 @@
       <c r="D1" t="s">
         <v>4</v>
       </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1486,18 +1566,18 @@
       </c>
       <c r="B2">
         <f>C2+D2+E2</f>
-        <v>125.73424759999999</v>
+        <v>77.861544439999989</v>
       </c>
       <c r="C2">
-        <f>[1]aromatics!$C$2</f>
-        <v>28.22</v>
+        <f>[1]ethylene!$C$2</f>
+        <v>17.311999999999998</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <f>[1]aromatics!$F$2</f>
-        <v>97.51424759999999</v>
+        <f>[1]ethylene!$F$2</f>
+        <v>60.549544439999998</v>
       </c>
     </row>
   </sheetData>
@@ -1506,6 +1586,98 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E8AD12-9E83-480C-A5ED-7437CA098876}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:E2)</f>
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>C2+D2+E2</f>
+        <v>125.73424759999999</v>
+      </c>
+      <c r="C2">
+        <f>[1]aromatics!$C$2</f>
+        <v>28.22</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>[1]aromatics!$F$2</f>
+        <v>97.51424759999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29673ED1-9CB7-4138-9690-7BF4F2B649AC}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1529,14 +1701,16 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <f>C2+D2+F2</f>
-        <v>12</v>
+        <f>SUM(C2:E2)</f>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <f>7-D2</f>
+        <v>0.33999999999999986</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <f>6.66</f>
+        <v>6.66</v>
       </c>
     </row>
   </sheetData>
@@ -1544,9 +1718,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="56.42578125" customWidth="1"/>
@@ -1556,31 +1730,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" t="s">
         <v>94</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>95</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>96</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>97</v>
-      </c>
-      <c r="G1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1609,19 +1783,19 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I3">
         <v>2014</v>
       </c>
       <c r="J3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1638,19 +1812,19 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I4">
         <v>2020</v>
       </c>
       <c r="J4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1715,19 +1889,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I12">
         <v>2014</v>
       </c>
       <c r="J12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1744,19 +1918,19 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I13">
         <v>2020</v>
       </c>
       <c r="J13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1810,19 +1984,19 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I19">
         <v>2014</v>
       </c>
       <c r="J19" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1839,19 +2013,19 @@
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H20" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I20">
         <v>2020</v>
       </c>
       <c r="J20" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1902,10 +2076,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>39</v>
@@ -1914,10 +2088,10 @@
         <v>2017</v>
       </c>
       <c r="J26" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K26" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1932,7 +2106,7 @@
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1940,28 +2114,28 @@
         <v>9</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I29">
         <v>2014</v>
       </c>
       <c r="J29" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K29" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1977,10 +2151,10 @@
         <v>12</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2"/>
     </row>
@@ -1989,7 +2163,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -2004,14 +2178,14 @@
         <v>12</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2019,33 +2193,33 @@
         <v>36</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I36">
         <v>2014</v>
       </c>
       <c r="J36" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K36" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2060,50 +2234,50 @@
         <v>9</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G39" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I39">
         <v>2014</v>
       </c>
       <c r="J39" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K39" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2111,12 +2285,12 @@
         <v>20</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -2131,44 +2305,44 @@
         <v>9</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G47" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I47">
         <v>2014</v>
       </c>
       <c r="J47" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K47" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2183,41 +2357,41 @@
         <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G52" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I52">
         <v>2014</v>
       </c>
       <c r="J52" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K52" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -2232,31 +2406,31 @@
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G57" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H57" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I57">
         <v>2014</v>
       </c>
       <c r="J57" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K57" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2264,24 +2438,24 @@
     </row>
     <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2296,47 +2470,47 @@
         <v>9</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G62" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H62" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I62">
         <v>2014</v>
       </c>
       <c r="J62" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K62" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -2351,31 +2525,31 @@
         <v>9</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G67" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H67" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I67">
         <v>2014</v>
       </c>
       <c r="J67" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K67" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2383,49 +2557,49 @@
         <v>10</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2433,22 +2607,22 @@
         <v>20</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
       <c r="E76" s="14"/>
     </row>
-    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -2456,58 +2630,124 @@
         <v>9</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F77" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G77" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H77" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I77">
         <v>2020</v>
       </c>
       <c r="J77" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K77" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E78" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
+      <c r="B79" t="s">
         <v>116</v>
       </c>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
+      <c r="D79" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E79" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="14"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F82" t="s">
+        <v>121</v>
+      </c>
+      <c r="G82" t="s">
+        <v>122</v>
+      </c>
+      <c r="H82" t="s">
+        <v>123</v>
+      </c>
+      <c r="I82">
+        <v>2017</v>
+      </c>
+      <c r="J82" t="s">
+        <v>100</v>
+      </c>
+      <c r="K82" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" t="s">
         <v>12</v>
       </c>
-      <c r="C80" t="s">
-        <v>85</v>
-      </c>
-      <c r="D80" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="3"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="3"/>
+      <c r="C85" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B88" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2529,9 +2769,10 @@
     <hyperlink ref="E26" r:id="rId16" xr:uid="{343544D7-B644-49AA-A279-42458BB4E4D5}"/>
     <hyperlink ref="E67" r:id="rId17" xr:uid="{582EC26F-4A9C-43A2-AF67-35BC4A09367A}"/>
     <hyperlink ref="E68" r:id="rId18" xr:uid="{618E33B2-BA08-4D38-911F-D038C60DBE22}"/>
+    <hyperlink ref="E82" r:id="rId19" xr:uid="{2605CA8D-2B51-451A-AEE4-6307769462A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>
 
@@ -2641,15 +2882,16 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>50.6</v>
+        <f>C2+D2</f>
+        <v>54.5</v>
       </c>
       <c r="C2">
-        <f>B2*[1]alu_prim!$C$2/[1]alu_prim!$B$2</f>
-        <v>47.617090319091396</v>
+        <f>52.2*50.6/(52.2+3.27)+5.76*3.9/12.96</f>
+        <v>49.35042365242473</v>
       </c>
       <c r="D2">
-        <f>B2*[1]alu_prim!$D$2/[1]alu_prim!$B$2</f>
-        <v>2.9829096809085991</v>
+        <f>3.27*50.6/(52.2+3.27)+7.2*3.9/12.96</f>
+        <v>5.1495763475752661</v>
       </c>
     </row>
   </sheetData>
@@ -2686,15 +2928,15 @@
       </c>
       <c r="B2">
         <f>C2+D2</f>
-        <v>10.8</v>
+        <v>6.4</v>
       </c>
       <c r="C2">
-        <f>[1]alu_sec!$C$2</f>
-        <v>1.8</v>
+        <f>1.8*2.5/(1.8+9)+5.76*3.9/12.96</f>
+        <v>2.15</v>
       </c>
       <c r="D2">
-        <f>[1]alu_sec!$D$2</f>
-        <v>9</v>
+        <f>9*2.5/(1.8+9)+7.2*3.9/12.96</f>
+        <v>4.25</v>
       </c>
     </row>
   </sheetData>
